--- a/examples/excel/charts.xlsx
+++ b/examples/excel/charts.xlsx
@@ -3,9 +3,9 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Analysis" sheetId="2" r:id="Rb6072b1ba3eb4df9"/>
-    <x:sheet name="StockData" sheetId="3" r:id="Re0f7873769744b44"/>
-    <x:sheet name="Assessment" sheetId="4" r:id="Rb4649b6ee473439f"/>
+    <x:sheet name="Analysis" sheetId="2" r:id="Rf74baf23fd474248"/>
+    <x:sheet name="StockData" sheetId="3" r:id="Rdc6db63004734218"/>
+    <x:sheet name="Assessment" sheetId="4" r:id="R4d25e253b6004d63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1825,7 +1825,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R862a8633a8a844d9"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R5f32f03e341a48f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1855,7 +1855,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R362fd87a32c44909"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R0fb89e79ac47438c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1885,7 +1885,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R11a3688d26e14787"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rc37ea2ed1d234d65"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1915,7 +1915,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R7210dec1daca4db2"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R9b97efaab64c4fc2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1950,7 +1950,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R6f313a028861415f"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R4f37a44f2dcb4bd4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1980,7 +1980,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R4caa4257730b4aed"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R8f38dfd91aa145ec"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2015,7 +2015,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rfac269e8bb84429b"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rfe978a6e5704422d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2050,7 +2050,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rdc457f110c054664"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R52fc8db431e44d06"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2059,8 +2059,117 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
@@ -2323,12 +2432,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4925c3cef0e64295"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R606676e2adee466a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="11" t="str">
@@ -2555,12 +2664,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a556a014e174a2f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccb94887c4c54494"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="12" t="str">
@@ -2983,12 +3092,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c81da26fe24bc9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd10e8f633b474643"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="19" t="str">
@@ -3117,6 +3226,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a49207658cb4c4a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88830dcb4140437a"/>
 </x:worksheet>
 </file>